--- a/output/pdf_financials_xlsx/TUNG.xlsx
+++ b/output/pdf_financials_xlsx/TUNG.xlsx
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.091497</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.08611199999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.513761</v>
       </c>
     </row>
     <row r="93">
@@ -2915,7 +2915,11 @@
           <t>Share-based payments reserve 5</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -2944,7 +2948,11 @@
           <t>Warrants reserve 6</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -3225,7 +3233,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.059813</v>
       </c>
@@ -3254,7 +3266,11 @@
           <t>Warrants reserve 8</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>0.031684</v>
       </c>

--- a/output/pdf_financials_xlsx/TUNG.xlsx
+++ b/output/pdf_financials_xlsx/TUNG.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.110462</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.622663</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.252783</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.110462</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.622663</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.252783</v>
       </c>
     </row>
     <row r="37">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/TUNG.xlsx
+++ b/output/pdf_financials_xlsx/TUNG.xlsx
@@ -2083,13 +2083,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010475</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001184</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.021638</v>
       </c>
     </row>
     <row r="102">
@@ -2163,13 +2163,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-0.010475</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-0.001184</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-0.021638</v>
       </c>
     </row>
     <row r="107">
@@ -3367,7 +3367,11 @@
           <t>Increase in GST/HST receivable</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>-0.010475</v>
       </c>
